--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$82</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>A organização adota controles mínimos na fase preparatória das contratações de TIC, com processo definido e análise técnica pela unidade competente?</t>
+          <t>A organização adota processo formal e padronizado para a fase preparatória das contratações de TIC, com responsabilidades definidas, análise técnica pela área de TIC e alinhamento aos instrumentos de planejamento?</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1701,8 +1701,72 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AJ-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA03/S3.5</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem previsão orçamentária demonstrada; encaminhamento exigia estimativa dos recursos e memória ou referência</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Plano de TIC não utilizado como referência para a elaboração da proposta orçamentária e do plano de contratações. Encaminhamento: integre o plano de TIC à elaboração da proposta orçamentária e do plano de contratações, de maneira proporcional ao porte, à estrutura e à capacidade de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Alinha a situação e o encaminhamento ao conteúdo efetivamente verificado por q2102ext[C], sem exigir estimativa orçamentária ou memória de cálculo não avaliadas pelo questionário.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AJ-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA06/Q6</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>A organização adota controles mínimos na fase preparatória das contratações de TIC, com processo definido e análise técnica pela unidade competente?</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>A organização adota processo formal e padronizado para a fase preparatória das contratações de TIC, com responsabilidades definidas, análise técnica pela área de TIC e alinhamento aos instrumentos de planejamento?</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Substitui expressão genérica por requisitos verificáveis e cobre processo formal e padronizado, responsabilidades, análise técnica e alinhamento ao planejamento.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4467,16 +4531,20 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC sem previsão orçamentária demonstrada.</t>
+          <t>Plano de TIC não utilizado como referência para a elaboração da proposta orçamentária e do plano de contratações.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-27</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+        <v>-106</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Sem ocorrência na base pós-comentários</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,9 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Contratações de TIC sem designação de Equipe de Planejamento com integrante técnico da área de TIC.</t>
+          <t>Contratações de TIC sem designação de equipe de planejamento com integrante técnico da área de TIC.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S2.3/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S2.1/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024. Ressalva de aplicação: Aplicável somente se a entidade declarou possuir Comitê.</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.1. Ressalva de aplicação: Monitorar o desempenho da TI com base em indicadores e metas pressupõe objetivos, indicadores e metas estabelecidos pela alta administração.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.1/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.4/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: Admitir instrumento equivalente a PDTI/PEDTIC, desde que satisfaça o resultado.</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3. Ressalva de aplicação: O processo estruturado do PDTI determinado contempla objetivos, indicadores e metas de TI alinhados aos objetivos de negócio.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.2/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.5/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: A aprovação deve ser pela instância competente, sem impor colegiado específico.</t>
+          <t>Lei nº 14.133/2021, art. 12, VII e § 1º; Acórdão TCE-RJ nº 44.490/2024, item II.3. Ressalva de aplicação: Integração do plano de TIC à proposta orçamentária e ao PCA, observado o condicionamento legal 'quando elaborado'.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.6/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S2.3/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024, item II.3.5. Ressalva de aplicação: Vincular a obrigação ao plano efetivamente adotado.</t>
+          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024. Ressalva de aplicação: Aplicável somente se a entidade declarou possuir Comitê.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S4.6/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.1/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 117. Ressalva de aplicação: Art. 117 exige fiscalização, não quadro próprio de TIC; regra calibrada para terceirização e ausência total de capacidade interna.</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: Admitir instrumento equivalente a PDTI/PEDTIC, desde que satisfaça o resultado.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S5.3/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.2/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 50. Ressalva de aplicação: A LGPD impõe segurança, mas não nomeia inventário; encaminhamento deve exigir resultado equivalente e proporcional ao tratamento de dados.</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: A aprovação deve ser pela instância competente, sem impor colegiado específico.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S5.5/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.6/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 48. Ressalva de aplicação: Art. 48 alcança incidentes com risco ou dano relevante; a rotina deve contemplar essa qualificação.</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3.5. Ressalva de aplicação: Vincular a obrigação ao plano efetivamente adotado.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S6.1/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S4.6/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 19, IV. Ressalva de aplicação: Art. 19, IV dirige-se aos órgãos com competência regulamentar; para os demais, exigir adoção de modelos aplicáveis, próprios ou compartilhados.</t>
+          <t>Lei nº 14.133/2021, art. 117. Ressalva de aplicação: Art. 117 exige fiscalização, não quadro próprio de TIC; regra calibrada para terceirização e ausência total de capacidade interna.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S6.3/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S5.3/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 12, VII, e 18. Ressalva de aplicação: A compatibilização com o PCA é obrigatória quando o plano tiver sido elaborado.</t>
+          <t>LGPD, arts. 46 e 50. Ressalva de aplicação: A LGPD impõe segurança, mas não nomeia inventário; encaminhamento deve exigir resultado equivalente e proporcional ao tratamento de dados.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1645,22 +1645,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mapa/Ações removidas</t>
+          <t>Mapa e matriz/S6.1/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV87, AV88, AV90, AV94, AV99, AV100, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
+          <t>Recomendação</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Excluídas da versão pós-comentários</t>
+          <t>Determinação</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Ações órfãs, pertencentes às situações retiradas ou incompatíveis com as regras calibradas.</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 19, IV. Ressalva de aplicação: Art. 19, IV dirige-se aos órgãos com competência regulamentar; para os demais, exigir adoção de modelos aplicáveis, próprios ou compartilhados.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1672,27 +1672,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AJ-038</t>
+          <t>AJ-037</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S1.2 × S2.1</t>
+          <t>Mapa/Ações removidas</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>q0103D e q1001C podiam gerar situações distintas pelo mesmo fato</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV87, AV88, AV90, AV94, AV99, AV100, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>S1.2 mantém competências formais por q0103; S2.1 usa somente q1001H (AV08/AV86)</t>
+          <t>Excluídas da versão pós-comentários</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Elimina sobreposição entre competência formal da área de TIC e direção estratégica exercida pela alta administração.</t>
+          <t>Ações órfãs, pertencentes às situações retiradas ou incompatíveis com as regras calibradas.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1704,27 +1704,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AJ-039</t>
+          <t>AJ-038</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA03/S3.5</t>
+          <t>Mapa e matriz/S1.2 × S2.1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC sem previsão orçamentária demonstrada; encaminhamento exigia estimativa dos recursos e memória ou referência</t>
+          <t>q0103D e q1001C podiam gerar situações distintas pelo mesmo fato</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC não utilizado como referência para a elaboração da proposta orçamentária e do plano de contratações. Encaminhamento: integre o plano de TIC à elaboração da proposta orçamentária e do plano de contratações, de maneira proporcional ao porte, à estrutura e à capacidade de planejamento da organização</t>
+          <t>S1.2 mantém competências formais por q0103; S2.1 usa somente q1001H (AV08/AV86)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Alinha a situação e o encaminhamento ao conteúdo efetivamente verificado por q2102ext[C], sem exigir estimativa orçamentária ou memória de cálculo não avaliadas pelo questionário.</t>
+          <t>Elimina sobreposição entre competência formal da área de TIC e direção estratégica exercida pela alta administração.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1736,37 +1736,549 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>AJ-038</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/S6.3/tipo de encaminhamento</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Recomendação</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Determinação</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Lei nº 14.133/2021, arts. 12, VII, e 18. Ressalva de aplicação: A compatibilização com o PCA é obrigatória quando o plano tiver sido elaborado.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AJ-039</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA03/S3.5</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Plano de TIC sem previsão orçamentária demonstrada; encaminhamento exigia estimativa dos recursos e memória ou referência</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Plano de TIC não utilizado como referência para a elaboração da proposta orçamentária e do plano de contratações. Encaminhamento: integre o plano de TIC à elaboração da proposta orçamentária e do plano de contratações, de maneira proporcional ao porte, à estrutura e à capacidade de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Alinha a situação e o encaminhamento ao conteúdo efetivamente verificado por q2102ext[C], sem exigir estimativa orçamentária ou memória de cálculo não avaliadas pelo questionário.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>AJ-040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Mapa e matriz/PA06/Q6</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>A organização adota controles mínimos na fase preparatória das contratações de TIC, com processo definido e análise técnica pela unidade competente?</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>A organização adota processo formal e padronizado para a fase preparatória das contratações de TIC, com responsabilidades definidas, análise técnica pela área de TIC e alinhamento aos instrumentos de planejamento?</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Substitui expressão genérica por requisitos verificáveis e cobre processo formal e padronizado, responsabilidades, análise técnica e alinhamento ao planejamento.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Aplicado</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>AJ-041</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/Q1, Q3 e Q4/identificadores</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Referências e situações renumeradas para eliminar lacunas</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Restaurar IR/P/E originais; S3.4, S3.5, S3.6 e S4.6</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Identificadores de auditoria são estáveis; a retirada de conteúdo deve preservar as lacunas e a rastreabilidade histórica.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>AJ-042</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/PA02/S2.3</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Somente negativa declaratória de q1001ext[F]</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>q1001ext[E] = Sim e (q1001ext[F] != Sim ou evidência de atuação insuficiente)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Reproduz conceitualmente a fórmula AV12 &amp; (AV13 | AV91) já utilizada no mapa.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>AJ-043</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/Procedimentos de Auditoria/PA04</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Descrição anterior de Q4 com perfis profissionais e competências</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Descrição vigente da Q4 com força de trabalho, funções e vínculos</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Mantém identidade entre a questão da matriz e a descrição do procedimento operacional.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>AJ-044</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA04/S4.3</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de cargos ou funções formalmente atribuídos à TIC ou à segurança da informação.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Limita a descrição ao conteúdo efetivamente testado por q2708[B] e q2708[D].</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>AJ-045</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/PA01/S1.3</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>itens_questionario: [q0102, q0102evi]</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>itens_questionario: [q0102]</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Remove referência residual a evidência que não integra IR, procedimento, evidência nem ação de verificação da situação.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>AJ-046</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/PA04/S4.1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Indentação inconsistente nos campos da situação</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Indentação uniforme dos campos e regras</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Preserva a estrutura documental e evita ambiguidade de leitura ou processamento.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>AJ-047</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/Motivos do Relatório/MR062</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Menção também à estrutura central externa</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Menção somente à execução predominantemente terceirizada</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>AV45 aceita exclusivamente o modelo q0101=B; o motivo deve descrever o mesmo gatilho.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>AJ-048</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/Motivos do Relatório/MR063</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Quantitativo interno insuficiente</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de profissionais internos de TIC</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>AV46 testa total interno exatamente igual a zero, e não insuficiência quantitativa.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>AJ-049</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/Q3/C5</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Critério legal específico ausente</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>C5: Lei nº 14.133/2021, art. 12, inciso VII e § 1º - Planejamento das contratações: o Plano de Contratações Anual, quando elaborado, deve alinhar-se ao planejamento estratégico, subsidiar a elaboração das leis orçamentárias e ser observado nas licitações e na execução contratual.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Acrescenta à Q3 fundamento legal específico sobre integração entre PCA, planejamento estratégico e leis orçamentárias.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>AJ-050</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA03/S3.4-S3.5</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>S3.4: [C3, C4]; S3.5: [C2, C3, C4]</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>S3.4: [C1, C3, C4]; S3.5: [C2, C4, C5]</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Limita cada situação a três critérios diretamente relacionados ao respectivo objeto; em S3.5, substitui o C3 pelo fundamento legal C5.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>AJ-051</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/Q4/C12-C13</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Critérios jurisprudenciais específicos sobre força de trabalho de TIC ausentes</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>C12: Acórdão 1.411/2014-TCU-Plenário, item 9.1.6.5 - O PDTI deve contemplar o quantitativo necessário ou ideal para a força de trabalho em TI. C13: Acórdão 1.411/2014-TCU-Plenário, item 9.1.7 - A organização deve adotar providências para dotar o setor de TI de quantitativo adequado às necessidades de trabalho em TI, consideradas as necessidades das demais áreas.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Cria identificadores novos para não reutilizar C3 e C4 removidos e preserva a rastreabilidade histórica.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>AJ-052</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA04/S4.1-S4.2</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>S4.1: [C2, C9]; S4.2: [C5, C9]</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>S4.1: [C2, C13]; S4.2: [C5, C12]</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Substitui o critério ISO genérico por precedentes do TCU diretamente aderentes à existência e ao dimensionamento da força de trabalho de TIC.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>AJ-053</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA01/Q1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Escopo amplo das atribuições, C4 em S1.2 e título genérico do achado</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Gestão da TIC como núcleo; S1.2 com [C2, C7]; achado sobre formalização, definição e posicionamento</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Restringe a Q1 ao mínimo essencial efetivamente testado e mantém correspondência entre subquestão, informação requerida, procedimento, evidência, situação e critério.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AJ-054</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA01/S1.1-S1.3</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>S1.1 e S1.2 como determinação; encaminhamentos anteriores de S1.2 e S1.3</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Todas as situações da Q1 como recomendação; encaminhamentos revisados</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Os gatilhos são predominantemente declaratórios ou apoiados em referenciais de boa prática e preservam espaço para solução organizacional proporcional.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F41"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2014,7 +2526,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>S1.1</t>
+          <t>S2.2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2029,19 +2541,19 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Lei nº 14.133/2021, art. 11, parágrafo único</t>
+          <t>Lei nº 14.133/2021, art. 11; Acórdãos TCE-RJ nº 44.490/2024 e TCU nº 1.411/2014</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Admitir estrutura equivalente; não impor criação de órgão por ato do jurisdicionado se houver reserva legal.</t>
+          <t>TCU 1.411/2014, item 9.1, é recomendação; TCE-RJ 44.490/2024 contém determinação para casos auditados.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>S1.2</t>
+          <t>S2.1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2056,19 +2568,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Lei nº 14.133/2021, art. 11, parágrafo único</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Exigir atribuições mínimas, não desenho organizacional único.</t>
+          <t>Monitorar o desempenho com base em indicadores e metas pressupõe objetivos, indicadores e metas estabelecidos.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>S2.2</t>
+          <t>S3.4</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2083,19 +2595,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 11; Acórdãos TCE-RJ nº 44.490/2024 e TCU nº 1.411/2014</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>TCU 1.411/2014, item 9.1, é recomendação; TCE-RJ 44.490/2024 contém determinação para casos auditados.</t>
+          <t>PDTI determinado contempla objetivos, indicadores e metas de TI alinhados aos objetivos de negócio.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S2.3</t>
+          <t>S3.5</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2110,19 +2622,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024</t>
+          <t>Lei nº 14.133/2021, art. 12, VII e § 1º; Acórdão TCE-RJ nº 44.490/2024, item II.3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Somente para quem declarou Comitê.</t>
+          <t>Integração do plano de TIC à proposta orçamentária e ao PCA, observado o condicionamento legal 'quando elaborado'.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>S3.1</t>
+          <t>S2.3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2137,19 +2649,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ</t>
+          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Admitir instrumento equivalente a PDTI/PEDTIC.</t>
+          <t>Somente para quem declarou Comitê.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S3.2</t>
+          <t>S3.1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2169,14 +2681,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Aprovação pela instância competente.</t>
+          <t>Admitir instrumento equivalente a PDTI/PEDTIC.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S3.6</t>
+          <t>S3.2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2191,19 +2703,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024, II.3.5</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Vincular ao plano adotado.</t>
+          <t>Aprovação pela instância competente.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>S4.6</t>
+          <t>S3.6</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2218,19 +2730,19 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 117</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, II.3.5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A norma impõe fiscalização, não quadro próprio; regra exige terceirização e zero de pessoal interno.</t>
+          <t>Vincular ao plano adotado.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S5.3</t>
+          <t>S4.6</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2245,19 +2757,19 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 50</t>
+          <t>Lei nº 14.133/2021, art. 117</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inventário é meio de demonstrar segurança/governança, não artefato nominal da LGPD.</t>
+          <t>A norma impõe fiscalização, não quadro próprio; regra exige terceirização e zero de pessoal interno.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S5.5</t>
+          <t>S5.3</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2272,12 +2784,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 48</t>
+          <t>LGPD, arts. 46 e 50</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Comunicação legal para incidentes com risco ou dano relevante.</t>
+          <t>Inventário é meio de demonstrar segurança/governança, não artefato nominal da LGPD.</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2848,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4315,16 +4827,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Área de TIC sem atribuições formalmente definidas ou sem atribuições formais de governança, planejamento ou gestão de TIC.</t>
+          <t>Área de TIC sem atribuições formalmente definidas ou sem atribuições formais de gestão de TIC.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>-55</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Sem ocorrência na base pós-comentários</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4639,24 +5155,28 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+          <t>Ausência de cargos ou funções formalmente atribuídos à TIC ou à segurança da informação.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+          <t>Ausência de cargos ou funções formalmente atribuídos à TIC ou à segurança da informação.</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Sem ocorrência na base pós-comentários</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4979,16 +5499,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Contratações de TIC sem designação de Equipe de Planejamento com integrante técnico da área de TIC.</t>
+          <t>Contratações de TIC sem designação de equipe de planejamento com integrante técnico da área de TIC.</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+        <v>-45</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Sem ocorrência na base pós-comentários</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Impacto da reexecução'!$A$1:$G$30</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-056</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-056</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-056</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S1.1/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S2.2/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Lei nº 14.133/2021, art. 11, parágrafo único. Ressalva de aplicação: Dever de resultado; admitir estrutura equivalente e observar a competência de auto-organização.</t>
+          <t>Decreto nº 12.198/2024, arts. 5º e 6º, § 2º; Acórdão TCE-RJ nº 44.490/2024, itens II.1, III.1 e V.1. Ressalva de aplicação: O Decreto é referência federal; a determinação se apoia também no precedente do TCE-RJ e deve admitir instância equivalente.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S1.2/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.4/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Lei nº 14.133/2021, art. 11, parágrafo único. Ressalva de aplicação: Exigir atribuições mínimas, sem impor desenho organizacional único.</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3. Ressalva de aplicação: O processo estruturado do PDTI determinado contempla objetivos, indicadores e metas de TI alinhados aos objetivos de negócio.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S2.2/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.5/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 11; Acórdãos TCE-RJ nº 44.490/2024 e TCU nº 1.411/2014. Ressalva de aplicação: O precedente TCE-RJ contém determinação; o precedente TCU citado contém recomendação.</t>
+          <t>Lei nº 14.133/2021, art. 12, VII e § 1º; Acórdão TCE-RJ nº 44.490/2024, item II.3. Ressalva de aplicação: Integração do plano de TIC à proposta orçamentária e ao PCA, observado o condicionamento legal 'quando elaborado'.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S2.1/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S2.3/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Acórdão TCE-RJ nº 44.490/2024, item II.1. Ressalva de aplicação: Monitorar o desempenho da TI com base em indicadores e metas pressupõe objetivos, indicadores e metas estabelecidos pela alta administração.</t>
+          <t>Decreto nº 12.198/2024, arts. 5º e 6º, § 2º; Acórdão TCE-RJ nº 44.490/2024, itens II.1, III.1 e V.1. Ressalva de aplicação: Aplicável somente se a entidade declarou possuir Comitê; a atuação exigida deve observar seu ato constitutivo.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.4/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.1/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3. Ressalva de aplicação: O processo estruturado do PDTI determinado contempla objetivos, indicadores e metas de TI alinhados aos objetivos de negócio.</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: Admitir instrumento equivalente a PDTI/PEDTIC, desde que satisfaça o resultado.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.5/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.2/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 12, VII e § 1º; Acórdão TCE-RJ nº 44.490/2024, item II.3. Ressalva de aplicação: Integração do plano de TIC à proposta orçamentária e ao PCA, observado o condicionamento legal 'quando elaborado'.</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: A aprovação deve ser pela instância competente, sem impor colegiado específico.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S2.3/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S3.6/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024. Ressalva de aplicação: Aplicável somente se a entidade declarou possuir Comitê.</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3.5. Ressalva de aplicação: Vincular a obrigação ao plano efetivamente adotado.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.1/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S4.6/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: Admitir instrumento equivalente a PDTI/PEDTIC, desde que satisfaça o resultado.</t>
+          <t>Lei nº 14.133/2021, art. 117. Ressalva de aplicação: Art. 117 exige fiscalização, não quadro próprio de TIC; regra calibrada para terceirização e ausência total de capacidade interna.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.2/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S5.3/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ. Ressalva de aplicação: A aprovação deve ser pela instância competente, sem impor colegiado específico.</t>
+          <t>LGPD, arts. 46 e 50. Ressalva de aplicação: A LGPD impõe segurança, mas não nomeia inventário; encaminhamento deve exigir resultado equivalente e proporcional ao tratamento de dados.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S3.6/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S6.1/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3.5. Ressalva de aplicação: Vincular a obrigação ao plano efetivamente adotado.</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 19, IV. Ressalva de aplicação: Art. 19, IV dirige-se aos órgãos com competência regulamentar; para os demais, exigir adoção de modelos aplicáveis, próprios ou compartilhados.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S4.6/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S6.3/tipo de encaminhamento</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 117. Ressalva de aplicação: Art. 117 exige fiscalização, não quadro próprio de TIC; regra calibrada para terceirização e ausência total de capacidade interna.</t>
+          <t>Lei nº 14.133/2021, arts. 12, VII, e 18. Ressalva de aplicação: A compatibilização com o PCA é obrigatória quando o plano tiver sido elaborado.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1608,27 +1608,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AJ-036</t>
+          <t>AJ-037</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S5.3/tipo de encaminhamento</t>
+          <t>Mapa/Ações removidas</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Recomendação</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV94, AV99, AV100, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Determinação</t>
+          <t>Excluídas da versão pós-comentários</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 50. Ressalva de aplicação: A LGPD impõe segurança, mas não nomeia inventário; encaminhamento deve exigir resultado equivalente e proporcional ao tratamento de dados.</t>
+          <t>Ações órfãs, pertencentes às situações retiradas ou incompatíveis com as regras calibradas.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1640,27 +1640,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AJ-037</t>
+          <t>AJ-038</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S6.1/tipo de encaminhamento</t>
+          <t>Mapa e matriz/S1.2 × S2.1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Recomendação</t>
+          <t>q0103D e q1001C podiam gerar situações distintas pelo mesmo fato</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Determinação</t>
+          <t>S1.2 mantém competências formais por q0103; S2.1 usa somente q1001H (AV08)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 19, IV. Ressalva de aplicação: Art. 19, IV dirige-se aos órgãos com competência regulamentar; para os demais, exigir adoção de modelos aplicáveis, próprios ou compartilhados.</t>
+          <t>Elimina sobreposição entre competência formal da área de TIC e direção estratégica exercida pela alta administração.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1672,27 +1672,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AJ-037</t>
+          <t>AJ-039</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mapa/Ações removidas</t>
+          <t>Mapa e matriz/PA03/S3.5</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV87, AV88, AV90, AV94, AV99, AV100, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
+          <t>Plano de TIC sem previsão orçamentária demonstrada; encaminhamento exigia estimativa dos recursos e memória ou referência</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Excluídas da versão pós-comentários</t>
+          <t>Plano de TIC não utilizado como referência para a elaboração da proposta orçamentária e do plano de contratações. Encaminhamento: integre o plano de TIC à elaboração da proposta orçamentária e do plano de contratações, de maneira proporcional ao porte, à estrutura e à capacidade de planejamento da organização</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ações órfãs, pertencentes às situações retiradas ou incompatíveis com as regras calibradas.</t>
+          <t>Alinha a situação e o encaminhamento ao conteúdo efetivamente verificado por q2102ext[C], sem exigir estimativa orçamentária ou memória de cálculo não avaliadas pelo questionário.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1704,27 +1704,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AJ-038</t>
+          <t>AJ-040</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S1.2 × S2.1</t>
+          <t>Mapa e matriz/PA06/Q6</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>q0103D e q1001C podiam gerar situações distintas pelo mesmo fato</t>
+          <t>A organização adota controles mínimos na fase preparatória das contratações de TIC, com processo definido e análise técnica pela unidade competente?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>S1.2 mantém competências formais por q0103; S2.1 usa somente q1001H (AV08/AV86)</t>
+          <t>A organização adota processo formal e padronizado para a fase preparatória das contratações de TIC, com responsabilidades definidas, análise técnica pela área de TIC e alinhamento aos instrumentos de planejamento?</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Elimina sobreposição entre competência formal da área de TIC e direção estratégica exercida pela alta administração.</t>
+          <t>Substitui expressão genérica por requisitos verificáveis e cobre processo formal e padronizado, responsabilidades, análise técnica e alinhamento ao planejamento.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1736,27 +1736,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AJ-038</t>
+          <t>AJ-041</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/S6.3/tipo de encaminhamento</t>
+          <t>Matriz/Q1, Q3 e Q4/identificadores</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Recomendação</t>
+          <t>Referências e situações renumeradas para eliminar lacunas</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Determinação</t>
+          <t>Restaurar IR/P/E originais; S3.4, S3.5, S3.6 e S4.6</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 12, VII, e 18. Ressalva de aplicação: A compatibilização com o PCA é obrigatória quando o plano tiver sido elaborado.</t>
+          <t>Identificadores de auditoria são estáveis; a retirada de conteúdo deve preservar as lacunas e a rastreabilidade histórica.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -1768,59 +1768,59 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AJ-039</t>
+          <t>AJ-042</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA03/S3.5</t>
+          <t>Matriz/PA02/S2.3</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC sem previsão orçamentária demonstrada; encaminhamento exigia estimativa dos recursos e memória ou referência</t>
+          <t>Somente negativa declaratória de q1001ext[F]</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC não utilizado como referência para a elaboração da proposta orçamentária e do plano de contratações. Encaminhamento: integre o plano de TIC à elaboração da proposta orçamentária e do plano de contratações, de maneira proporcional ao porte, à estrutura e à capacidade de planejamento da organização</t>
+          <t>q1001ext[E] = Sim e (q1001ext[F] != Sim ou evidência de atuação insuficiente)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Alinha a situação e o encaminhamento ao conteúdo efetivamente verificado por q2102ext[C], sem exigir estimativa orçamentária ou memória de cálculo não avaliadas pelo questionário.</t>
+          <t>Reproduz conceitualmente a fórmula AV12 &amp; (AV13 | AV91) já utilizada no mapa.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-056</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AJ-040</t>
+          <t>AJ-043</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA06/Q6</t>
+          <t>Mapa/Procedimentos de Auditoria/PA04</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A organização adota controles mínimos na fase preparatória das contratações de TIC, com processo definido e análise técnica pela unidade competente?</t>
+          <t>Descrição anterior de Q4 com perfis profissionais e competências</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>A organização adota processo formal e padronizado para a fase preparatória das contratações de TIC, com responsabilidades definidas, análise técnica pela área de TIC e alinhamento aos instrumentos de planejamento?</t>
+          <t>Descrição vigente da Q4 com força de trabalho, funções e vínculos</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Substitui expressão genérica por requisitos verificáveis e cobre processo formal e padronizado, responsabilidades, análise técnica e alinhamento ao planejamento.</t>
+          <t>Mantém identidade entre a questão da matriz e a descrição do procedimento operacional.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1832,27 +1832,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AJ-041</t>
+          <t>AJ-044</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Matriz/Q1, Q3 e Q4/identificadores</t>
+          <t>Mapa e matriz/PA04/S4.3</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Referências e situações renumeradas para eliminar lacunas</t>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Restaurar IR/P/E originais; S3.4, S3.5, S3.6 e S4.6</t>
+          <t>Ausência de cargos ou funções formalmente atribuídos à TIC ou à segurança da informação.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Identificadores de auditoria são estáveis; a retirada de conteúdo deve preservar as lacunas e a rastreabilidade histórica.</t>
+          <t>Limita a descrição ao conteúdo efetivamente testado por q2708[B] e q2708[D].</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -1864,27 +1864,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AJ-042</t>
+          <t>AJ-045</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Matriz/PA02/S2.3</t>
+          <t>Matriz/PA01/S1.3</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Somente negativa declaratória de q1001ext[F]</t>
+          <t>itens_questionario: [q0102, q0102evi]</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>q1001ext[E] = Sim e (q1001ext[F] != Sim ou evidência de atuação insuficiente)</t>
+          <t>itens_questionario: [q0102]</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Reproduz conceitualmente a fórmula AV12 &amp; (AV13 | AV91) já utilizada no mapa.</t>
+          <t>Remove referência residual a evidência que não integra IR, procedimento, evidência nem ação de verificação da situação.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -1896,27 +1896,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AJ-043</t>
+          <t>AJ-046</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Mapa/Procedimentos de Auditoria/PA04</t>
+          <t>Matriz/PA04/S4.1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Descrição anterior de Q4 com perfis profissionais e competências</t>
+          <t>Indentação inconsistente nos campos da situação</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Descrição vigente da Q4 com força de trabalho, funções e vínculos</t>
+          <t>Indentação uniforme dos campos e regras</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Mantém identidade entre a questão da matriz e a descrição do procedimento operacional.</t>
+          <t>Preserva a estrutura documental e evita ambiguidade de leitura ou processamento.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1928,27 +1928,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AJ-044</t>
+          <t>AJ-047</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA04/S4.3</t>
+          <t>Mapa/Motivos do Relatório/MR062</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação</t>
+          <t>Menção também à estrutura central externa</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ausência de cargos ou funções formalmente atribuídos à TIC ou à segurança da informação.</t>
+          <t>Menção somente à execução predominantemente terceirizada</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Limita a descrição ao conteúdo efetivamente testado por q2708[B] e q2708[D].</t>
+          <t>AV45 aceita exclusivamente o modelo q0101=B; o motivo deve descrever o mesmo gatilho.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -1960,27 +1960,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AJ-045</t>
+          <t>AJ-048</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Matriz/PA01/S1.3</t>
+          <t>Mapa/Motivos do Relatório/MR063</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>itens_questionario: [q0102, q0102evi]</t>
+          <t>Quantitativo interno insuficiente</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>itens_questionario: [q0102]</t>
+          <t>Ausência de profissionais internos de TIC</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Remove referência residual a evidência que não integra IR, procedimento, evidência nem ação de verificação da situação.</t>
+          <t>AV46 testa total interno exatamente igual a zero, e não insuficiência quantitativa.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -1992,27 +1992,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AJ-046</t>
+          <t>AJ-049</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Matriz/PA04/S4.1</t>
+          <t>Matriz/Q3/C5</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Indentação inconsistente nos campos da situação</t>
+          <t>Critério legal específico ausente</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Indentação uniforme dos campos e regras</t>
+          <t>C5: Lei nº 14.133/2021, art. 12, inciso VII e § 1º - Planejamento das contratações: o Plano de Contratações Anual, quando elaborado, deve alinhar-se ao planejamento estratégico, subsidiar a elaboração das leis orçamentárias e ser observado nas licitações e na execução contratual.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Preserva a estrutura documental e evita ambiguidade de leitura ou processamento.</t>
+          <t>Acrescenta à Q3 fundamento legal específico sobre integração entre PCA, planejamento estratégico e leis orçamentárias.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2024,27 +2024,27 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AJ-047</t>
+          <t>AJ-050</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Mapa/Motivos do Relatório/MR062</t>
+          <t>Mapa e matriz/PA03/S3.4-S3.5</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Menção também à estrutura central externa</t>
+          <t>S3.4: [C3, C4]; S3.5: [C2, C3, C4]</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Menção somente à execução predominantemente terceirizada</t>
+          <t>S3.4: [C1, C3, C4]; S3.5: [C2, C4, C5]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>AV45 aceita exclusivamente o modelo q0101=B; o motivo deve descrever o mesmo gatilho.</t>
+          <t>Limita cada situação a três critérios diretamente relacionados ao respectivo objeto; em S3.5, substitui o C3 pelo fundamento legal C5.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2056,27 +2056,27 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AJ-048</t>
+          <t>AJ-051</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Mapa/Motivos do Relatório/MR063</t>
+          <t>Matriz/Q4/C12-C13</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Quantitativo interno insuficiente</t>
+          <t>Critérios jurisprudenciais específicos sobre força de trabalho de TIC ausentes</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Ausência de profissionais internos de TIC</t>
+          <t>C12: Acórdão 1.411/2014-TCU-Plenário, item 9.1.6.5 - O PDTI deve contemplar o quantitativo necessário ou ideal para a força de trabalho em TI. C13: Acórdão 1.411/2014-TCU-Plenário, item 9.1.7 - A organização deve adotar providências para dotar o setor de TI de quantitativo adequado às necessidades de trabalho em TI, consideradas as necessidades das demais áreas.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>AV46 testa total interno exatamente igual a zero, e não insuficiência quantitativa.</t>
+          <t>Cria identificadores novos para não reutilizar C3 e C4 removidos e preserva a rastreabilidade histórica.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2088,27 +2088,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AJ-049</t>
+          <t>AJ-052</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Matriz/Q3/C5</t>
+          <t>Mapa e matriz/PA04/S4.1-S4.2</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Critério legal específico ausente</t>
+          <t>S4.1: [C2, C9]; S4.2: [C5, C9]</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>C5: Lei nº 14.133/2021, art. 12, inciso VII e § 1º - Planejamento das contratações: o Plano de Contratações Anual, quando elaborado, deve alinhar-se ao planejamento estratégico, subsidiar a elaboração das leis orçamentárias e ser observado nas licitações e na execução contratual.</t>
+          <t>S4.1: [C2, C13]; S4.2: [C5, C12]</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Acrescenta à Q3 fundamento legal específico sobre integração entre PCA, planejamento estratégico e leis orçamentárias.</t>
+          <t>Substitui o critério ISO genérico por precedentes do TCU diretamente aderentes à existência e ao dimensionamento da força de trabalho de TIC.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2120,27 +2120,27 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AJ-050</t>
+          <t>AJ-053</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA03/S3.4-S3.5</t>
+          <t>Mapa e matriz/PA01/Q1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>S3.4: [C3, C4]; S3.5: [C2, C3, C4]</t>
+          <t>Escopo amplo das atribuições, C4 em S1.2 e título genérico do achado</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>S3.4: [C1, C3, C4]; S3.5: [C2, C4, C5]</t>
+          <t>Gestão da TIC como núcleo; S1.2 com [C2, C7]; achado sobre formalização, definição e posicionamento</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Limita cada situação a três critérios diretamente relacionados ao respectivo objeto; em S3.5, substitui o C3 pelo fundamento legal C5.</t>
+          <t>Restringe a Q1 ao mínimo essencial efetivamente testado e mantém correspondência entre subquestão, informação requerida, procedimento, evidência, situação e critério.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2152,27 +2152,27 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AJ-051</t>
+          <t>AJ-054</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Matriz/Q4/C12-C13</t>
+          <t>Mapa e matriz/PA01/S1.1-S1.3</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Critérios jurisprudenciais específicos sobre força de trabalho de TIC ausentes</t>
+          <t>S1.1 e S1.2 como determinação; encaminhamentos anteriores de S1.2 e S1.3</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>C12: Acórdão 1.411/2014-TCU-Plenário, item 9.1.6.5 - O PDTI deve contemplar o quantitativo necessário ou ideal para a força de trabalho em TI. C13: Acórdão 1.411/2014-TCU-Plenário, item 9.1.7 - A organização deve adotar providências para dotar o setor de TI de quantitativo adequado às necessidades de trabalho em TI, consideradas as necessidades das demais áreas.</t>
+          <t>Todas as situações da Q1 como recomendação; encaminhamentos revisados</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Cria identificadores novos para não reutilizar C3 e C4 removidos e preserva a rastreabilidade histórica.</t>
+          <t>Os gatilhos são predominantemente declaratórios ou apoiados em referenciais de boa prática e preservam espaço para solução organizacional proporcional.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2184,27 +2184,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AJ-052</t>
+          <t>AJ-055</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA04/S4.1-S4.2</t>
+          <t>Mapa e matriz/PA02/Q2</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>S4.1: [C2, C9]; S4.2: [C5, C9]</t>
+          <t>Questão, riscos, critérios e encaminhamentos anteriores</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>S4.1: [C2, C13]; S4.2: [C5, C12]</t>
+          <t>Q2 revisada com C1 a C4 e foco em objetivos, composição e atuação do Comitê</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Substitui o critério ISO genérico por precedentes do TCU diretamente aderentes à existência e ao dimensionamento da força de trabalho de TIC.</t>
+          <t>Mantém apenas os elementos essenciais de governança efetivamente abrangidos pelos itens H, E e F da q1001.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2216,27 +2216,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AJ-053</t>
+          <t>AJ-056</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Mapa e matriz/PA01/Q1</t>
+          <t>Mapa e matriz/PA02/S2.1-S2.3</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Escopo amplo das atribuições, C4 em S1.2 e título genérico do achado</t>
+          <t>AV08 | AV86; AV11 | AV89; AV12 &amp; (AV13 | AV91)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Gestão da TIC como núcleo; S1.2 com [C2, C7]; achado sobre formalização, definição e posicionamento</t>
+          <t>AV08; AV11; AV12 &amp; AV13</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Restringe a Q1 ao mínimo essencial efetivamente testado e mantém correspondência entre subquestão, informação requerida, procedimento, evidência, situação e critério.</t>
+          <t>A decisão mais recente trata a avaliação documental como evidência de suporte, sem convertê-la em gatilho autônomo das situações; S2.1 retorna a recomendação.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2245,40 +2245,8 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>AJ-054</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Mapa e matriz/PA01/S1.1-S1.3</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>S1.1 e S1.2 como determinação; encaminhamentos anteriores de S1.2 e S1.3</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Todas as situações da Q1 como recomendação; encaminhamentos revisados</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Os gatilhos são predominantemente declaratórios ou apoiados em referenciais de boa prática e preservam espaço para solução organizacional proporcional.</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Aplicado</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2328,17 +2296,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Proposta anterior de restringir a situação a AV11 versus orientação de manter a avaliação documental AV89</t>
+          <t>Orientação anterior de manter AV89 como gatilho alternativo versus nova regra declaratória</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AV11 | AV89</t>
+          <t>AV11</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>A negativa declarada e a insuficiência da prova de instituição formal permanecem como gatilhos alternativos; a eventual concomitância com S2.3 deve ser interpretada como formalização não comprovada e atuação não comprovada.</t>
+          <t>Prevalece a decisão mais recente: a evidência documental permanece prevista na matriz como suporte, mas não gera autonomamente a situação.</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2541,19 +2509,19 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 11; Acórdãos TCE-RJ nº 44.490/2024 e TCU nº 1.411/2014</t>
+          <t>Decreto nº 12.198/2024, arts. 5º e 6º, § 2º; Acórdão TCE-RJ nº 44.490/2024, itens II.1, III.1 e V.1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>TCU 1.411/2014, item 9.1, é recomendação; TCE-RJ 44.490/2024 contém determinação para casos auditados.</t>
+          <t>O Decreto é referência federal; admitir Comitê ou instância equivalente compatível com a organização.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>S2.1</t>
+          <t>S3.4</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2568,19 +2536,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Acórdão TCE-RJ nº 44.490/2024, item II.1</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Monitorar o desempenho com base em indicadores e metas pressupõe objetivos, indicadores e metas estabelecidos.</t>
+          <t>PDTI determinado contempla objetivos, indicadores e metas de TI alinhados aos objetivos de negócio.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>S3.4</t>
+          <t>S3.5</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2595,19 +2563,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Acórdão TCE-RJ nº 44.490/2024, item II.3</t>
+          <t>Lei nº 14.133/2021, art. 12, VII e § 1º; Acórdão TCE-RJ nº 44.490/2024, item II.3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>PDTI determinado contempla objetivos, indicadores e metas de TI alinhados aos objetivos de negócio.</t>
+          <t>Integração do plano de TIC à proposta orçamentária e ao PCA, observado o condicionamento legal 'quando elaborado'.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S3.5</t>
+          <t>S2.3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2622,19 +2590,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 12, VII e § 1º; Acórdão TCE-RJ nº 44.490/2024, item II.3</t>
+          <t>Decreto nº 12.198/2024, arts. 5º e 6º, § 2º; Acórdão TCE-RJ nº 44.490/2024, itens II.1, III.1 e V.1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Integração do plano de TIC à proposta orçamentária e ao PCA, observado o condicionamento legal 'quando elaborado'.</t>
+          <t>Somente para quem declarou Comitê; observar as competências do ato constitutivo.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>S2.3</t>
+          <t>S3.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2649,19 +2617,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CF/88, art. 37; Acórdão TCE-RJ nº 44.490/2024</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Somente para quem declarou Comitê.</t>
+          <t>Admitir instrumento equivalente a PDTI/PEDTIC.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S3.1</t>
+          <t>S3.2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2681,14 +2649,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Admitir instrumento equivalente a PDTI/PEDTIC.</t>
+          <t>Aprovação pela instância competente.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S3.2</t>
+          <t>S3.6</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2703,19 +2671,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 18; precedentes TCU/TCE-RJ</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024, II.3.5</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Aprovação pela instância competente.</t>
+          <t>Vincular ao plano adotado.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>S3.6</t>
+          <t>S4.6</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -2730,19 +2698,19 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Acórdão TCE-RJ nº 44.490/2024, II.3.5</t>
+          <t>Lei nº 14.133/2021, art. 117</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Vincular ao plano adotado.</t>
+          <t>A norma impõe fiscalização, não quadro próprio; regra exige terceirização e zero de pessoal interno.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>S4.6</t>
+          <t>S5.3</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2757,19 +2725,19 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 117</t>
+          <t>LGPD, arts. 46 e 50</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A norma impõe fiscalização, não quadro próprio; regra exige terceirização e zero de pessoal interno.</t>
+          <t>Inventário é meio de demonstrar segurança/governança, não artefato nominal da LGPD.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>S5.3</t>
+          <t>S6.1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2784,19 +2752,19 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 50</t>
+          <t>Lei nº 14.133/2021, arts. 11 e 19, IV</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Inventário é meio de demonstrar segurança/governança, não artefato nominal da LGPD.</t>
+          <t>Art. 19, IV, tem destinatário qualificado; admitir modelos compartilhados aplicáveis.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>S6.1</t>
+          <t>S6.3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2811,44 +2779,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 19, IV</t>
+          <t>Lei nº 14.133/2021, arts. 12, VII, e 18</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Art. 19, IV, tem destinatário qualificado; admitir modelos compartilhados aplicáveis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S6.3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Recomendação</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Determinação</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Lei nº 14.133/2021, arts. 12, VII, e 18</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
           <t>Compatibilização com PCA quando elaborado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2859,7 +2800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3618,7 +3559,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AV87</t>
+          <t>AV86</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3635,7 +3576,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AV88</t>
+          <t>AV87</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3652,7 +3593,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AV90</t>
+          <t>AV88</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3669,7 +3610,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AV94</t>
+          <t>AV89</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3686,7 +3627,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AV99</t>
+          <t>AV90</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3703,7 +3644,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AV100</t>
+          <t>AV91</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3720,7 +3661,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AV102</t>
+          <t>AV94</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3737,7 +3678,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AV104</t>
+          <t>AV99</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3754,7 +3695,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AV106</t>
+          <t>AV100</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3771,7 +3712,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AV108</t>
+          <t>AV102</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3788,7 +3729,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AV109</t>
+          <t>AV104</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3805,7 +3746,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AV110</t>
+          <t>AV106</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3822,7 +3763,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AV111</t>
+          <t>AV108</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3839,7 +3780,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AV112</t>
+          <t>AV109</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3856,7 +3797,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AV113</t>
+          <t>AV110</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3873,7 +3814,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AV114</t>
+          <t>AV111</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3890,7 +3831,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AV115</t>
+          <t>AV112</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3907,7 +3848,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AV116</t>
+          <t>AV113</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3924,7 +3865,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AV117</t>
+          <t>AV114</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3941,7 +3882,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AV118</t>
+          <t>AV115</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3958,7 +3899,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AV119</t>
+          <t>AV116</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3975,7 +3916,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AV120</t>
+          <t>AV117</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3992,7 +3933,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AV121</t>
+          <t>AV118</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4009,7 +3950,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AV122</t>
+          <t>AV119</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4026,7 +3967,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AV123</t>
+          <t>AV120</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4043,7 +3984,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AV130</t>
+          <t>AV121</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4060,7 +4001,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AV131</t>
+          <t>AV122</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4077,7 +4018,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AV134</t>
+          <t>AV123</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4094,7 +4035,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AV135</t>
+          <t>AV130</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4111,7 +4052,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AV138</t>
+          <t>AV131</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4128,7 +4069,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AV139</t>
+          <t>AV134</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4145,7 +4086,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AV142</t>
+          <t>AV135</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4162,7 +4103,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AV144</t>
+          <t>AV138</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4179,7 +4120,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AV145</t>
+          <t>AV139</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4196,7 +4137,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AV146</t>
+          <t>AV142</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4213,7 +4154,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AV147</t>
+          <t>AV144</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4230,7 +4171,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AV149</t>
+          <t>AV145</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4247,22 +4188,73 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
           <t>AV151</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C82"/>
+  <autoFilter ref="A1:C85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4668,7 +4660,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>As 72 ações remanescentes são referenciadas nas fórmulas.</t>
+          <t>As 69 ações remanescentes são referenciadas nas fórmulas.</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4823,12 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Sem ocorrência na base pós-comentários</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4912,7 +4900,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Comitê de TIC ou instância equivalente não instituído formalmente.</t>
+          <t>Comitê de TIC ou instância equivalente não instituído formalmente ou sem representação de áreas relevantes da organização.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -5051,16 +5039,12 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Sem ocorrência na base pós-comentários</t>
-        </is>
-      </c>
+        <v>-27</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5167,16 +5151,12 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Sem ocorrência na base pós-comentários</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5503,16 +5483,12 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Sem ocorrência na base pós-comentários</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Impacto da reexecução'!$A$1:$G$30</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-057/AJ-058</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV94, AV99, AV100, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-057/AJ-058</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-057/AJ-058</t>
         </is>
       </c>
     </row>
@@ -2245,8 +2245,72 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AJ-057</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA03/Q3</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Questão, riscos, procedimentos, evidências e situações anteriores</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Q3 revisada com processo formal, plano vigente, aprovação, alinhamento, integração e acompanhamento</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Consolida a rastreabilidade da questão e preserva a lacuna S3.3, mantendo estáveis os identificadores das situações.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AJ-058</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/PA03/S3.1-S3.6</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Ações declaratórias e documentais sem gate comum de plano vigente</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>VT06 existe_plano_ti; S3.1 inclui AV154; S3.2-S3.6 exigem AV155</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Restringe as situações sobre atributos do plano às organizações que declararam plano vigente ao menos parcialmente adotado; evidências permanecem como suporte, sem gatilho autônomo.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F56"/>
+  <autoFilter ref="A1:F58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2257,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2423,27 +2487,49 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Q3/plano vigente</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Itens de detalhamento q2102ext aplicados mesmo quando não havia plano vigente</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>VT06 define existe_plano_ti; S3.2 a S3.6 dependem desse gate</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Evita imputar deficiências de aprovação, alinhamento, integração ou acompanhamento a quem ainda não possui plano vigente; nesses casos, aplica-se S3.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Natureza jurídica</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Determinação baseada em dever de resultado versus norma sem artefato nominal</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Determinação com equivalência funcional e proporcionalidade</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Evita transformar PDTI, Comitê ou inventário em modelo organizacional único quando o dever jurídico admite solução equivalente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2800,7 +2886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3661,7 +3747,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AV94</t>
+          <t>AV92</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3678,7 +3764,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AV99</t>
+          <t>AV93</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3695,7 +3781,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AV100</t>
+          <t>AV94</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3712,7 +3798,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AV102</t>
+          <t>AV95</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3729,7 +3815,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AV104</t>
+          <t>AV96</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3746,7 +3832,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AV106</t>
+          <t>AV97</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3763,7 +3849,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AV108</t>
+          <t>AV98</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3780,7 +3866,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AV109</t>
+          <t>AV99</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3797,7 +3883,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AV110</t>
+          <t>AV100</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3814,7 +3900,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AV111</t>
+          <t>AV101</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3831,7 +3917,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AV112</t>
+          <t>AV102</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3848,7 +3934,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AV113</t>
+          <t>AV104</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3865,7 +3951,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AV114</t>
+          <t>AV106</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3882,7 +3968,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AV115</t>
+          <t>AV108</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3899,7 +3985,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AV116</t>
+          <t>AV109</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3916,7 +4002,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AV117</t>
+          <t>AV110</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3933,7 +4019,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AV118</t>
+          <t>AV111</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3950,7 +4036,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AV119</t>
+          <t>AV112</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3967,7 +4053,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AV120</t>
+          <t>AV113</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3984,7 +4070,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AV121</t>
+          <t>AV114</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4001,7 +4087,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AV122</t>
+          <t>AV115</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4018,7 +4104,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AV123</t>
+          <t>AV116</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4035,7 +4121,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AV130</t>
+          <t>AV117</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4052,7 +4138,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AV131</t>
+          <t>AV118</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4069,7 +4155,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AV134</t>
+          <t>AV119</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4086,7 +4172,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AV135</t>
+          <t>AV120</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4103,7 +4189,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AV138</t>
+          <t>AV121</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4120,7 +4206,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AV139</t>
+          <t>AV122</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4137,7 +4223,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AV142</t>
+          <t>AV123</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4154,7 +4240,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AV144</t>
+          <t>AV130</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4171,7 +4257,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AV145</t>
+          <t>AV131</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4188,7 +4274,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AV146</t>
+          <t>AV134</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4205,7 +4291,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AV147</t>
+          <t>AV135</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4222,7 +4308,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AV149</t>
+          <t>AV138</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4239,22 +4325,141 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>AV139</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>AV142</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>AV144</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>AV145</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
           <t>AV151</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C85"/>
+  <autoFilter ref="A1:C92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4422,7 +4627,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Eliminar variáveis temporárias não usadas</t>
+          <t>Eliminar variáveis temporárias não usadas e criar o gate do plano</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4432,7 +4637,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Somente total_TI e total_TI_interno permanecem.</t>
+          <t>Permanecem total_TI, total_TI_interno e existe_plano_ti.</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4865,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>As 69 ações remanescentes são referenciadas nas fórmulas.</t>
+          <t>As 64 ações remanescentes são referenciadas nas fórmulas.</t>
         </is>
       </c>
     </row>
@@ -4954,7 +5159,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+          <t>Inexistência ou insuficiência do processo de planejamento de TIC para produzir e manter plano de TIC adequado.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -4985,10 +5190,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
     </row>
@@ -5012,10 +5217,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -5039,10 +5244,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-27</v>
+        <v>-90</v>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
     </row>
@@ -5062,14 +5267,14 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ausência de acompanhamento, revisão ou atualização periódica do plano de TIC.</t>
+          <t>Ausência de acompanhamento da execução do plano de TIC.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -5510,10 +5715,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1727</v>
+        <v>1476</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-369</v>
+        <v>-620</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Impacto da reexecução'!$A$1:$G$30</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-059/AJ-060</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV103, AV104, AV105, AV106, AV107, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-059/AJ-060</t>
         </is>
       </c>
     </row>
@@ -2309,8 +2309,72 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AJ-059</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA04/Q4</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Questão, riscos, critérios e situações anteriores</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Q4 revisada com foco em estruturação, dimensionamento, funções e capacidade interna nos modelos terceirizados</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Delimita a questão aos mecanismos mínimos efetivamente testados e incorpora o C14 como precedente específico do TCE-RJ.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>AJ-060</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/PA04/S4.1-S4.6</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>AV26 aceitava todo modelo diferente de F; AV103/AV105/AV107 eram gatilhos; S4.6 era determinação</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>AV26 restrito a A/B/D/E; retirada dos gatilhos documentais; S4.6 como recomendação</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Exclui o modelo centralizado externo de S4.1, trata evidências documentais como suporte e reconhece que a regra de S4.6 indica oportunidade de melhoria sem comprovar irregularidade concreta de fiscalização.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F58"/>
+  <autoFilter ref="A1:F60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2426,17 +2490,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Determinação por falta de fiscalização versus predomínio de terceiros como gatilho</t>
+          <t>Determinação por falta de fiscalização versus regra que testa apenas terceirização e ausência de pessoal interno</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>q0101B &amp; total_TI_interno=0</t>
+          <t>q0101B &amp; total_TI_interno=0, com recomendação</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Predomínio, isoladamente, não prova infração ao art. 117; modelo C é legítimo.</t>
+          <t>A condição indica risco de insuficiência de capacidade interna, mas não comprova irregularidade concreta na fiscalização; o C14 sustenta avaliação proporcional.</t>
         </is>
       </c>
     </row>
@@ -2774,22 +2838,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>Determinação</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Recomendação</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Determinação</t>
-        </is>
-      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, art. 117</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024-PLEN, itens I.10.11, III.9.11 e IV.11.3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A norma impõe fiscalização, não quadro próprio; regra exige terceirização e zero de pessoal interno.</t>
+          <t>A regra demonstra risco de capacidade interna, mas não comprova descumprimento concreto do dever de fiscalização.</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3934,7 +3998,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AV104</t>
+          <t>AV103</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3951,7 +4015,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AV106</t>
+          <t>AV104</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3968,7 +4032,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AV108</t>
+          <t>AV105</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3985,7 +4049,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AV109</t>
+          <t>AV106</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4002,7 +4066,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AV110</t>
+          <t>AV107</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4019,7 +4083,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AV111</t>
+          <t>AV108</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4036,7 +4100,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AV112</t>
+          <t>AV109</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4053,7 +4117,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AV113</t>
+          <t>AV110</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4070,7 +4134,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AV114</t>
+          <t>AV111</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4087,7 +4151,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AV115</t>
+          <t>AV112</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4104,7 +4168,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AV116</t>
+          <t>AV113</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4121,7 +4185,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AV117</t>
+          <t>AV114</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4138,7 +4202,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AV118</t>
+          <t>AV115</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4155,7 +4219,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AV119</t>
+          <t>AV116</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4172,7 +4236,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AV120</t>
+          <t>AV117</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4189,7 +4253,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AV121</t>
+          <t>AV118</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4206,7 +4270,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AV122</t>
+          <t>AV119</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4223,7 +4287,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AV123</t>
+          <t>AV120</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4240,7 +4304,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AV130</t>
+          <t>AV121</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4257,7 +4321,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AV131</t>
+          <t>AV122</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4274,7 +4338,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AV134</t>
+          <t>AV123</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4291,7 +4355,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AV135</t>
+          <t>AV130</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4308,7 +4372,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AV138</t>
+          <t>AV131</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4325,7 +4389,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AV139</t>
+          <t>AV134</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4342,7 +4406,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AV142</t>
+          <t>AV135</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4359,7 +4423,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AV144</t>
+          <t>AV138</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,7 +4440,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AV145</t>
+          <t>AV139</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4393,7 +4457,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AV146</t>
+          <t>AV142</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4410,7 +4474,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AV147</t>
+          <t>AV144</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4427,7 +4491,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AV149</t>
+          <t>AV145</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4444,22 +4508,73 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>AV151</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C92"/>
+  <autoFilter ref="A1:C95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4865,7 +4980,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>As 64 ações remanescentes são referenciadas nas fórmulas.</t>
+          <t>As 61 ações remanescentes são referenciadas nas fórmulas.</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5440,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
+          <t>Ausência ou insuficiência de definição documentada do quantitativo necessário de pessoal de TIC e segurança da informação.</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -5441,7 +5556,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Dependência externa relevante sem capacidade interna suficiente para coordenar e fiscalizar a TIC.</t>
+          <t>Operação de TIC predominantemente terceirizada sem profissionais internos de TIC.</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Impacto da reexecução'!$A$1:$G$30</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-061/AJ-062</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-061/AJ-062</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV103, AV104, AV105, AV106, AV107, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV134, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV103, AV104, AV105, AV106, AV107, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV124, AV125, AV126, AV127, AV128, AV129, AV130, AV131, AV132, AV133, AV134, AV135, AV136, AV137, AV138, AV139, AV140, AV141, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2373,8 +2373,72 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>AJ-061</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA05/Q5</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Questão, riscos, critérios, procedimentos e situações anteriores</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Q5 revisada com catálogo, níveis de serviço, inventário de ativos, gestão de configuração e incidentes</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Mantém apenas as práticas mínimas efetivamente testadas, explicita a rastreabilidade e incorpora referências específicas do TCE-RJ e da ABNT NBR ISO/IEC 20000-2:2021.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>AJ-062</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/PA05/S5.1-S5.5</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Evidências documentais como gatilhos autônomos; q2203A em S5.3; S5.3 como determinação</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Regras declaratórias; q2504A/B em S5.3; q2203A/C em S5.4; todas as situações como recomendação</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Trata as evidências como suporte, separa inventário de ativos da gestão de configuração e ajusta a natureza dos encaminhamentos aos referenciais predominantemente orientadores.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F60"/>
+  <autoFilter ref="A1:F62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2385,7 +2449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2507,93 +2571,115 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>S6.1</t>
+          <t>S5.3 × S5.4</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Exigir q2801B com painel sem a coluna</t>
+          <t>q2203A tratado como inventário de ativos versus conteúdo de base consolidada de configurações</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Painel vigente ampliado com B e metadados</t>
+          <t>q2504A/B em S5.3; q2203A/C em S5.4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Foram materializados 21 registros não conformes já avaliados; nenhum resultado foi inventado.</t>
+          <t>O inventário de dispositivos e softwares permanece distinto da base de itens de configuração e de seus relacionamentos; as evidências documentais apoiam a validação, mas não são gatilhos autônomos.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S1.2 × S2.1</t>
+          <t>S6.1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>q0103D e q1001C mediam, em grande parte, a mesma formalização de responsabilidades</t>
+          <t>Exigir q2801B com painel sem a coluna</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>S1.2 conserva q0103D; S2.1 passa a usar somente q1001H</t>
+          <t>Painel vigente ampliado com B e metadados</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Distingue competência formal da unidade de direção estratégica por objetivos, indicadores e metas.</t>
+          <t>Foram materializados 21 registros não conformes já avaliados; nenhum resultado foi inventado.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Q3/plano vigente</t>
+          <t>S1.2 × S2.1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Itens de detalhamento q2102ext aplicados mesmo quando não havia plano vigente</t>
+          <t>q0103D e q1001C mediam, em grande parte, a mesma formalização de responsabilidades</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>VT06 define existe_plano_ti; S3.2 a S3.6 dependem desse gate</t>
+          <t>S1.2 conserva q0103D; S2.1 passa a usar somente q1001H</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Evita imputar deficiências de aprovação, alinhamento, integração ou acompanhamento a quem ainda não possui plano vigente; nesses casos, aplica-se S3.1.</t>
+          <t>Distingue competência formal da unidade de direção estratégica por objetivos, indicadores e metas.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Q3/plano vigente</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Itens de detalhamento q2102ext aplicados mesmo quando não havia plano vigente</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>VT06 define existe_plano_ti; S3.2 a S3.6 dependem desse gate</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Evita imputar deficiências de aprovação, alinhamento, integração ou acompanhamento a quem ainda não possui plano vigente; nesses casos, aplica-se S3.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Natureza jurídica</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Determinação baseada em dever de resultado versus norma sem artefato nominal</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Determinação com equivalência funcional e proporcionalidade</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Evita transformar PDTI, Comitê ou inventário em modelo organizacional único quando o dever jurídico admite solução equivalente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2865,22 +2951,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Determinação</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Recomendação</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Determinação</t>
-        </is>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>LGPD, arts. 46 e 50</t>
+          <t>Acórdão TCE-RJ nº 44.490/2024-PLEN, itens II.7.5, III.9.5 e V.6.2 – Recomendações quanto à gestão de configuração e ativos de TIC, incluindo formalização do processo e manutenção de base consolidada de ativos e itens de configuração.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inventário é meio de demonstrar segurança/governança, não artefato nominal da LGPD.</t>
+          <t>O precedente formula recomendações e o gatilho declaratório não demonstra, por si só, descumprimento de dever legal expresso.</t>
         </is>
       </c>
     </row>
@@ -2950,7 +3036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4355,7 +4441,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AV130</t>
+          <t>AV124</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4372,7 +4458,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AV131</t>
+          <t>AV125</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4389,7 +4475,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AV134</t>
+          <t>AV126</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4406,7 +4492,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AV135</t>
+          <t>AV127</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4423,7 +4509,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AV138</t>
+          <t>AV128</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4440,7 +4526,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AV139</t>
+          <t>AV129</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4457,7 +4543,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AV142</t>
+          <t>AV130</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4474,7 +4560,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AV144</t>
+          <t>AV131</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4491,7 +4577,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AV145</t>
+          <t>AV132</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4508,7 +4594,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AV146</t>
+          <t>AV133</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4525,7 +4611,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AV147</t>
+          <t>AV134</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4542,7 +4628,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AV149</t>
+          <t>AV135</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4559,22 +4645,226 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>AV136</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>AV137</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>AV138</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>AV139</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>AV140</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>AV141</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>AV142</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>AV144</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>AV145</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>AV146</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
           <t>AV151</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C95"/>
+  <autoFilter ref="A1:C107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4980,7 +5270,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>As 61 ações remanescentes são referenciadas nas fórmulas.</t>
+          <t>As 49 ações remanescentes são referenciadas nas fórmulas.</t>
         </is>
       </c>
     </row>
@@ -5637,14 +5927,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+          <t>Inventário e controle de dispositivos e softwares de TIC inexistente ou insuficiente.</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
@@ -5668,10 +5958,10 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
@@ -5830,10 +6120,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1476</v>
+        <v>1467</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-620</v>
+        <v>-629</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Impacto da reexecução'!$A$1:$G$30</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-063/AJ-064</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-063/AJ-064</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-063/AJ-064</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Superado por AJ-063/AJ-064</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV103, AV104, AV105, AV106, AV107, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV124, AV125, AV126, AV127, AV128, AV129, AV130, AV131, AV132, AV133, AV134, AV135, AV136, AV137, AV138, AV139, AV140, AV141, AV142, AV144, AV145, AV146, AV147, AV149, AV151</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV80, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV103, AV104, AV105, AV106, AV107, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV124, AV125, AV126, AV127, AV128, AV129, AV130, AV131, AV132, AV133, AV134, AV135, AV136, AV137, AV138, AV139, AV140, AV141, AV142, AV143, AV144, AV145, AV146, AV147, AV148, AV149, AV150, AV151, AV153</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2437,8 +2437,72 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>AJ-063</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Mapa e matriz/PA06/Q6</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Questão, riscos, critérios, procedimentos e situações anteriores</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Q6 revisada com processo padronizado, análise técnica, alinhamento ao planejamento e equipe de planejamento</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Consolida os elementos mínimos da fase preparatória e mantém correspondência direta entre subquestões, riscos, informações requeridas, procedimentos, evidências e situações.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>AJ-064</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/PA06/S6.1-S6.4</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Gatilhos documentais autônomos; S6.3 também acionada por q2802ext[C]; S6.1 como determinação</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>AV73 | AV152 | AV78 | AV82 | AV83; S6.3 acionada somente por q2804[B]; S6.1 como recomendação</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Mantém as evidências como suporte, elimina dupla medição do alinhamento ao PCA e adequa o tipo de S6.1 à natureza declaratória da regra e aos referenciais utilizados.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F62"/>
+  <autoFilter ref="A1:F64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2449,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2593,93 +2657,115 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>S6.1</t>
+          <t>S6.3</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Exigir q2801B com painel sem a coluna</t>
+          <t>q2802ext[C] e q2804[B] como gatilhos cumulativos de alinhamento</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Painel vigente ampliado com B e metadados</t>
+          <t>Somente q2804[B] gera S6.3; q2802ext[C] e q2802evi permanecem como suporte</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Foram materializados 21 registros não conformes já avaliados; nenhum resultado foi inventado.</t>
+          <t>q2804[B] verifica diretamente se as contratações executadas estavam previstas nos instrumentos vigentes; evita imputação adicional pelo modo de elaboração do PCA.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>S1.2 × S2.1</t>
+          <t>S6.1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>q0103D e q1001C mediam, em grande parte, a mesma formalização de responsabilidades</t>
+          <t>Exigir q2801B com painel sem a coluna</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>S1.2 conserva q0103D; S2.1 passa a usar somente q1001H</t>
+          <t>Painel vigente ampliado com B e metadados</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Distingue competência formal da unidade de direção estratégica por objetivos, indicadores e metas.</t>
+          <t>Foram materializados 21 registros não conformes já avaliados; nenhum resultado foi inventado.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Q3/plano vigente</t>
+          <t>S1.2 × S2.1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Itens de detalhamento q2102ext aplicados mesmo quando não havia plano vigente</t>
+          <t>q0103D e q1001C mediam, em grande parte, a mesma formalização de responsabilidades</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>VT06 define existe_plano_ti; S3.2 a S3.6 dependem desse gate</t>
+          <t>S1.2 conserva q0103D; S2.1 passa a usar somente q1001H</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Evita imputar deficiências de aprovação, alinhamento, integração ou acompanhamento a quem ainda não possui plano vigente; nesses casos, aplica-se S3.1.</t>
+          <t>Distingue competência formal da unidade de direção estratégica por objetivos, indicadores e metas.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Q3/plano vigente</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Itens de detalhamento q2102ext aplicados mesmo quando não havia plano vigente</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>VT06 define existe_plano_ti; S3.2 a S3.6 dependem desse gate</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Evita imputar deficiências de aprovação, alinhamento, integração ou acompanhamento a quem ainda não possui plano vigente; nesses casos, aplica-se S3.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Natureza jurídica</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Determinação baseada em dever de resultado versus norma sem artefato nominal</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Determinação com equivalência funcional e proporcionalidade</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Evita transformar PDTI, Comitê ou inventário em modelo organizacional único quando o dever jurídico admite solução equivalente.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D10"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2978,22 +3064,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Determinação</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>Recomendação</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Determinação</t>
-        </is>
-      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 11 e 19, IV</t>
+          <t>Lei nº 14.133/2021, art. 11, parágrafo único: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos. Lei nº 14.133/2021, art. 19, inciso IV: instituição de modelos de minutas de editais, termos de referência, contratos padronizados e demais documentos. Acórdão nº 2.342/2016-TCU-Plenário, item 9.1.7 – Precedente quanto à definição, aprovação e formalização de processo de trabalho para o planejamento de cada contratação, com controles internos mínimos.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Art. 19, IV, tem destinatário qualificado; admitir modelos compartilhados aplicáveis.</t>
+          <t>O gatilho é declaratório e os critérios admitem modelos institucionais ou centralizados e fluxos proporcionais.</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3101,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lei nº 14.133/2021, arts. 12, VII, e 18</t>
+          <t>Lei nº 14.133/2021, art. 11, parágrafo único: responsabilidade da alta administração pela governança das contratações, com processos, estruturas, gestão de riscos e controles internos. Lei nº 14.133/2021, arts. 12, VII e §1º, e 18, caput e §1º, II – a fase preparatória deve compatibilizar-se com o Plano de Contratações Anual, quando elaborado, e deve ser demonstrado o alinhamento da contratação com o planejamento da Administração. Acórdão TCE-RJ nº 44.490/2024-PLEN, itens III.7 e IV.9 – Determinações para estruturação do processo de planejamento anual das contratações, contemplando consolidação das demandas, participação das áreas, aprovação e publicidade do plano.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Compatibilização com PCA quando elaborado.</t>
+          <t>Compatibilização com o PCA quando elaborado, admitidos ajustes ou justificativas em casos excepcionais.</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3761,7 +3847,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AV81</t>
+          <t>AV80</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3778,7 +3864,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AV85</t>
+          <t>AV81</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3795,7 +3881,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AV86</t>
+          <t>AV85</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3812,7 +3898,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AV87</t>
+          <t>AV86</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3829,7 +3915,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AV88</t>
+          <t>AV87</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3846,7 +3932,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AV89</t>
+          <t>AV88</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3863,7 +3949,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AV90</t>
+          <t>AV89</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3880,7 +3966,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AV91</t>
+          <t>AV90</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3897,7 +3983,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AV92</t>
+          <t>AV91</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3914,7 +4000,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AV93</t>
+          <t>AV92</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3931,7 +4017,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AV94</t>
+          <t>AV93</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3948,7 +4034,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AV95</t>
+          <t>AV94</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3965,7 +4051,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AV96</t>
+          <t>AV95</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3982,7 +4068,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AV97</t>
+          <t>AV96</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3999,7 +4085,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AV98</t>
+          <t>AV97</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4016,7 +4102,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AV99</t>
+          <t>AV98</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4033,7 +4119,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AV100</t>
+          <t>AV99</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4050,7 +4136,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AV101</t>
+          <t>AV100</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4067,7 +4153,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AV102</t>
+          <t>AV101</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4084,7 +4170,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AV103</t>
+          <t>AV102</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4101,7 +4187,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AV104</t>
+          <t>AV103</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4118,7 +4204,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AV105</t>
+          <t>AV104</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4135,7 +4221,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AV106</t>
+          <t>AV105</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4152,7 +4238,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AV107</t>
+          <t>AV106</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4169,7 +4255,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AV108</t>
+          <t>AV107</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4186,7 +4272,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AV109</t>
+          <t>AV108</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4203,7 +4289,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AV110</t>
+          <t>AV109</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4220,7 +4306,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AV111</t>
+          <t>AV110</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4237,7 +4323,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AV112</t>
+          <t>AV111</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4254,7 +4340,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AV113</t>
+          <t>AV112</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4271,7 +4357,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AV114</t>
+          <t>AV113</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4288,7 +4374,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AV115</t>
+          <t>AV114</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4305,7 +4391,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AV116</t>
+          <t>AV115</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4322,7 +4408,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AV117</t>
+          <t>AV116</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4339,7 +4425,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AV118</t>
+          <t>AV117</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4356,7 +4442,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AV119</t>
+          <t>AV118</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4373,7 +4459,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AV120</t>
+          <t>AV119</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4390,7 +4476,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AV121</t>
+          <t>AV120</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4407,7 +4493,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AV122</t>
+          <t>AV121</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4424,7 +4510,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AV123</t>
+          <t>AV122</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4441,7 +4527,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AV124</t>
+          <t>AV123</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4458,7 +4544,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AV125</t>
+          <t>AV124</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4475,7 +4561,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AV126</t>
+          <t>AV125</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4492,7 +4578,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AV127</t>
+          <t>AV126</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4509,7 +4595,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AV128</t>
+          <t>AV127</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4526,7 +4612,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AV129</t>
+          <t>AV128</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4543,7 +4629,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AV130</t>
+          <t>AV129</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4560,7 +4646,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AV131</t>
+          <t>AV130</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4577,7 +4663,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AV132</t>
+          <t>AV131</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4594,7 +4680,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AV133</t>
+          <t>AV132</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4611,7 +4697,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AV134</t>
+          <t>AV133</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4628,7 +4714,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AV135</t>
+          <t>AV134</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4645,7 +4731,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AV136</t>
+          <t>AV135</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4662,7 +4748,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>AV137</t>
+          <t>AV136</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4679,7 +4765,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AV138</t>
+          <t>AV137</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4696,7 +4782,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AV139</t>
+          <t>AV138</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4713,7 +4799,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AV140</t>
+          <t>AV139</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4730,7 +4816,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AV141</t>
+          <t>AV140</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4747,7 +4833,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AV142</t>
+          <t>AV141</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -4764,7 +4850,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AV144</t>
+          <t>AV142</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -4781,7 +4867,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AV145</t>
+          <t>AV143</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -4798,7 +4884,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AV146</t>
+          <t>AV144</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -4815,7 +4901,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AV147</t>
+          <t>AV145</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -4832,7 +4918,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AV149</t>
+          <t>AV146</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -4849,22 +4935,107 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>AV147</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>AV148</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>AV149</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>AV150</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>AV151</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>AV153</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Removida da versão pós-comentários</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C107"/>
+  <autoFilter ref="A1:C112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5270,7 +5441,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>As 49 ações remanescentes são referenciadas nas fórmulas.</t>
+          <t>As 44 ações remanescentes são referenciadas nas fórmulas.</t>
         </is>
       </c>
     </row>
@@ -6066,10 +6237,10 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-6</v>
+        <v>-73</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
@@ -6120,10 +6291,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1467</v>
+        <v>1400</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-629</v>
+        <v>-696</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
@@ -6147,10 +6318,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-21</v>
+        <v>-26</v>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
     </row>

--- a/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
+++ b/docs/revisao-mapa/ajustes-mapa-verificacao-achados-pos-comentarios-gestor-2026-08-17.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto da reexecução" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ajustes'!$A$1:$F$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contradições resolvidas'!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Encaminhamentos'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ações removidas'!$A$1:$C$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ordem de implementação'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Validações'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Impacto da reexecução'!$A$1:$G$30</definedName>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV80, AV81, AV85, AV86, AV87, AV88, AV89, AV90, AV91, AV92, AV93, AV94, AV95, AV96, AV97, AV98, AV99, AV100, AV101, AV102, AV103, AV104, AV105, AV106, AV107, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV124, AV125, AV126, AV127, AV128, AV129, AV130, AV131, AV132, AV133, AV134, AV135, AV136, AV137, AV138, AV139, AV140, AV141, AV142, AV143, AV144, AV145, AV146, AV147, AV148, AV149, AV150, AV151, AV153</t>
+          <t>AV07, AV09, AV10, AV16, AV21, AV22, AV23, AV27, AV28, AV30, AV32, AV34, AV35, AV36, AV37, AV38, AV39, AV40, AV41, AV42, AV43, AV44, AV47, AV48, AV49, AV50, AV51, AV52, AV53, AV60, AV61, AV64, AV65, AV68, AV69, AV72, AV74, AV75, AV76, AV77, AV79, AV80, AV81, AV85, AV87, AV88, AV94, AV99, AV100, AV102, AV104, AV106, AV108, AV109, AV110, AV111, AV112, AV113, AV114, AV115, AV116, AV117, AV118, AV119, AV120, AV121, AV122, AV123, AV130, AV131, AV135, AV138, AV139, AV142, AV144, AV145, AV146, AV147, AV149, AV150, AV151</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Parcialmente superado por AJ-065/AJ-066</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Parcialmente superado por AJ-065/AJ-066</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Parcialmente superado por AJ-065/AJ-066</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Aplicado</t>
+          <t>Parcialmente superado por AJ-065/AJ-066</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,76 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
+          <t>Parcialmente superado por AJ-065/AJ-066</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>AJ-065</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Mapa/Ações de avaliação documental</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Somente AV84 participava das fórmulas do mapa revisado</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Restaurar AV86, AV89-AV93, AV95-AV98, AV101, AV103, AV105, AV107, AV124-AV129, AV132-AV134, AV136, AV137, AV140, AV141, AV143 e AV148; incluir AV153</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Reincorpora a validação documental das práticas essenciais expressamente selecionadas pela equipe e inclui q2801ext[B] no planejamento das contratações.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>Aplicado</t>
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>AJ-066</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Matriz/Q2-Q6/regras de identificação</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Avaliações documentais descritas apenas como suporte</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Regras passam a considerar resultado documental Não conforme nos itens selecionados</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Sincroniza a matriz com as fórmulas operacionais e preserva, em S2.3, gate que impede dupla imputação quando a própria instituição do Comitê não foi comprovada.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Aplicado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F64"/>
+  <autoFilter ref="A1:F66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3122,7 +3186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3898,7 +3962,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AV86</t>
+          <t>AV87</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3915,7 +3979,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AV87</t>
+          <t>AV88</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3932,7 +3996,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AV88</t>
+          <t>AV94</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3949,7 +4013,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AV89</t>
+          <t>AV99</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3966,7 +4030,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AV90</t>
+          <t>AV100</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3983,7 +4047,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AV91</t>
+          <t>AV102</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4000,7 +4064,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AV92</t>
+          <t>AV104</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4017,7 +4081,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AV93</t>
+          <t>AV106</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4034,7 +4098,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AV94</t>
+          <t>AV108</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4051,7 +4115,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AV95</t>
+          <t>AV109</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -4068,7 +4132,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AV96</t>
+          <t>AV110</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -4085,7 +4149,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AV97</t>
+          <t>AV111</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4102,7 +4166,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AV98</t>
+          <t>AV112</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4119,7 +4183,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AV99</t>
+          <t>AV113</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4136,7 +4200,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AV100</t>
+          <t>AV114</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4153,7 +4217,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AV101</t>
+          <t>AV115</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4170,7 +4234,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AV102</t>
+          <t>AV116</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4187,7 +4251,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AV103</t>
+          <t>AV117</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4204,7 +4268,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AV104</t>
+          <t>AV118</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4221,7 +4285,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AV105</t>
+          <t>AV119</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4238,7 +4302,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AV106</t>
+          <t>AV120</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4255,7 +4319,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AV107</t>
+          <t>AV121</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4272,7 +4336,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AV108</t>
+          <t>AV122</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4289,7 +4353,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AV109</t>
+          <t>AV123</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4306,7 +4370,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AV110</t>
+          <t>AV130</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4323,7 +4387,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AV111</t>
+          <t>AV131</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4340,7 +4404,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AV112</t>
+          <t>AV135</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4357,7 +4421,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AV113</t>
+          <t>AV138</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4374,7 +4438,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AV114</t>
+          <t>AV139</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4391,7 +4455,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AV115</t>
+          <t>AV142</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4408,7 +4472,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AV116</t>
+          <t>AV144</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4425,7 +4489,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AV117</t>
+          <t>AV145</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4442,7 +4506,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AV118</t>
+          <t>AV146</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4459,7 +4523,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>AV119</t>
+          <t>AV147</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4476,7 +4540,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AV120</t>
+          <t>AV149</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4493,7 +4557,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AV121</t>
+          <t>AV150</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4510,7 +4574,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AV122</t>
+          <t>AV151</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4524,518 +4588,8 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>AV123</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>AV124</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>AV125</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>AV126</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>AV127</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>AV128</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>AV129</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>AV130</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>AV131</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>AV132</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>AV133</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>AV134</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>AV135</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>AV136</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>AV137</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>AV138</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>AV139</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>AV140</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>AV141</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>AV142</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>AV143</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>AV144</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>AV145</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>AV146</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>AV147</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>AV148</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>AV149</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>AV150</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>AV151</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>AV153</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Removida da versão pós-comentários</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Órfã, pertencente a S4.4/S4.5 ou excluída por calibração/desacoplamento da regra.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C112"/>
+  <autoFilter ref="A1:C82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5441,7 +4995,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>As 44 ações remanescentes são referenciadas nas fórmulas.</t>
+          <t>As 74 ações remanescentes são referenciadas nas fórmulas.</t>
         </is>
       </c>
     </row>
@@ -5712,10 +5266,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
@@ -5766,10 +5320,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-62</v>
+        <v>-57</v>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
     </row>
@@ -5793,10 +5347,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-63</v>
+        <v>-56</v>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
@@ -5820,10 +5374,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-90</v>
+        <v>-86</v>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
     </row>
@@ -5847,10 +5401,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-63</v>
+        <v>-58</v>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
@@ -6098,14 +5652,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Inventário e controle de dispositivos e softwares de TIC inexistente ou insuficiente.</t>
+          <t>Inventário e controle de ativos e configurações de TIC inexistente ou insuficiente.</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
@@ -6183,10 +5737,10 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
@@ -6291,10 +5845,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1400</v>
+        <v>1435</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-696</v>
+        <v>-661</v>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
